--- a/data/P1/P1T3_BQ7.xlsx
+++ b/data/P1/P1T3_BQ7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76B74A0-0394-0E42-9C9B-59C276F992A5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC0BAA1-35FA-6D4A-855F-DFADFC4BF3BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29700" yWindow="4160" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="29700" yWindow="4160" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -220,13 +220,124 @@
   </si>
   <si>
     <t>建築物緊緊地靠在一起。</t>
+  </si>
+  <si>
+    <t>phonetics</t>
+  </si>
+  <si>
+    <t>syllable</t>
+  </si>
+  <si>
+    <t>/ˈbɪldɪŋ/</t>
+  </si>
+  <si>
+    <t>build-ing</t>
+  </si>
+  <si>
+    <t>/ˈneɪbəhʊd/</t>
+  </si>
+  <si>
+    <t>neigh-bor-hood</t>
+  </si>
+  <si>
+    <t>/taʊn/</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>/ˈsɪti/</t>
+  </si>
+  <si>
+    <t>cit-y</t>
+  </si>
+  <si>
+    <t>/ˈkʌntri/</t>
+  </si>
+  <si>
+    <t>coun-try</t>
+  </si>
+  <si>
+    <t>/əˈpɑːtmənt/</t>
+  </si>
+  <si>
+    <t>a-part-ment</t>
+  </si>
+  <si>
+    <t>/dɪˈpɑːtmənt stɔː(r)/</t>
+  </si>
+  <si>
+    <t>de-part-ment store</t>
+  </si>
+  <si>
+    <t>/ˈrestərɒnt/</t>
+  </si>
+  <si>
+    <t>res-tau-rant</t>
+  </si>
+  <si>
+    <t>/həʊˈtel/</t>
+  </si>
+  <si>
+    <t>ho-tel</t>
+  </si>
+  <si>
+    <t>/ˈhɒspɪtl/</t>
+  </si>
+  <si>
+    <t>hos-pi-tal</t>
+  </si>
+  <si>
+    <t>/ˈklɪnɪk/</t>
+  </si>
+  <si>
+    <t>clin-ic</t>
+  </si>
+  <si>
+    <t>/ˈsuːpəmɑːkɪt/</t>
+  </si>
+  <si>
+    <t>su-per-mar-ket</t>
+  </si>
+  <si>
+    <t>/ˈnɔɪzi/</t>
+  </si>
+  <si>
+    <t>nois-y</t>
+  </si>
+  <si>
+    <t>/ˈkwaɪət/</t>
+  </si>
+  <si>
+    <t>qui-et</t>
+  </si>
+  <si>
+    <t>/seɪf/</t>
+  </si>
+  <si>
+    <t>/ˈdeɪndʒərəs/</t>
+  </si>
+  <si>
+    <t>dan-ger-ous</t>
+  </si>
+  <si>
+    <t>/ˈbɔːrɪŋ/</t>
+  </si>
+  <si>
+    <t>bor-ing</t>
+  </si>
+  <si>
+    <t>/ˈɪntrəstɪŋ/</t>
+  </si>
+  <si>
+    <t>in-ter-est-ing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -275,6 +386,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -284,12 +403,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -298,7 +432,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -315,6 +449,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -631,14 +768,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -648,10 +788,18 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="D1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" ht="16">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" ht="16">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -661,10 +809,15 @@
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" t="s">
+        <v>66</v>
+      </c>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="16">
+    </row>
+    <row r="3" spans="1:10" ht="16">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
@@ -674,8 +827,14 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="16">
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -685,8 +844,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="16">
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -696,8 +861,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="16">
+      <c r="D5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -707,8 +878,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="16">
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16">
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
@@ -718,8 +895,14 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="16">
+      <c r="D7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -729,8 +912,14 @@
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="16">
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="16">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -740,8 +929,14 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="16">
+      <c r="D9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16">
       <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
@@ -751,8 +946,14 @@
       <c r="C10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="16">
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16">
       <c r="A11" s="5" t="s">
         <v>16</v>
       </c>
@@ -762,8 +963,14 @@
       <c r="C11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="16">
+      <c r="D11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16">
       <c r="A12" s="5" t="s">
         <v>17</v>
       </c>
@@ -773,8 +980,14 @@
       <c r="C12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="16">
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -784,8 +997,14 @@
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="16">
+      <c r="D13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16">
       <c r="A14" s="5" t="s">
         <v>18</v>
       </c>
@@ -795,8 +1014,14 @@
       <c r="C14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="16">
+      <c r="D14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16">
       <c r="A15" s="5" t="s">
         <v>19</v>
       </c>
@@ -806,8 +1031,14 @@
       <c r="C15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="16">
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="16">
       <c r="A16" s="5" t="s">
         <v>20</v>
       </c>
@@ -817,8 +1048,14 @@
       <c r="C16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="16">
+      <c r="D16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16">
       <c r="A17" s="5" t="s">
         <v>21</v>
       </c>
@@ -828,8 +1065,14 @@
       <c r="C17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="16">
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16">
       <c r="A18" s="5" t="s">
         <v>22</v>
       </c>
@@ -839,8 +1082,14 @@
       <c r="C18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="16">
+      <c r="D18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16">
       <c r="A19" s="5" t="s">
         <v>23</v>
       </c>
@@ -850,26 +1099,32 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:5">
       <c r="A21" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:5">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>

--- a/data/P1/P1T3_BQ7.xlsx
+++ b/data/P1/P1T3_BQ7.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC0BAA1-35FA-6D4A-855F-DFADFC4BF3BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58653B65-95DC-8545-A20F-8ACAC4ADC0D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29700" yWindow="4160" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="32220" yWindow="2260" windowWidth="30480" windowHeight="17020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="119">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -331,6 +331,64 @@
   </si>
   <si>
     <t>in-ter-est-ing</t>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tall structure with walls and rooms for people</t>
+  </si>
+  <si>
+    <t>The area around your home with many houses</t>
+  </si>
+  <si>
+    <t>A small place with houses, shops and streets</t>
+  </si>
+  <si>
+    <t>A big place with lots of tall buildings and people</t>
+  </si>
+  <si>
+    <t>A large land area with its own rules and people</t>
+  </si>
+  <si>
+    <t>A small home inside a tall building</t>
+  </si>
+  <si>
+    <t>A big shop selling clothes, toys and many things</t>
+  </si>
+  <si>
+    <t>A place where you go to eat food</t>
+  </si>
+  <si>
+    <t>A place for visitors to sleep and rest</t>
+  </si>
+  <si>
+    <t>A place doctors help sick or hurt people</t>
+  </si>
+  <si>
+    <t>A small place to see doctors for minor sickness</t>
+  </si>
+  <si>
+    <t>A big shop full of food and daily things</t>
+  </si>
+  <si>
+    <t>Full of loud sounds, hard to rest</t>
+  </si>
+  <si>
+    <t>With little or no loud noise</t>
+  </si>
+  <si>
+    <t>No harm, you do not need to worry</t>
+  </si>
+  <si>
+    <t>Can hurt you, not safe</t>
+  </si>
+  <si>
+    <t>Not fun, makes you feel tired</t>
+  </si>
+  <si>
+    <t>Fun to watch, read or play with</t>
   </si>
 </sst>
 </file>
@@ -794,7 +852,9 @@
       <c r="E1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -815,6 +875,9 @@
       <c r="E2" t="s">
         <v>66</v>
       </c>
+      <c r="F2" t="s">
+        <v>101</v>
+      </c>
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:10" ht="16">
@@ -833,6 +896,9 @@
       <c r="E3" t="s">
         <v>68</v>
       </c>
+      <c r="F3" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="16">
       <c r="A4" s="5" t="s">
@@ -850,6 +916,9 @@
       <c r="E4" t="s">
         <v>70</v>
       </c>
+      <c r="F4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="5" t="s">
@@ -867,6 +936,9 @@
       <c r="E5" t="s">
         <v>72</v>
       </c>
+      <c r="F5" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="16">
       <c r="A6" s="5" t="s">
@@ -884,6 +956,9 @@
       <c r="E6" t="s">
         <v>74</v>
       </c>
+      <c r="F6" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="16">
       <c r="A7" s="5" t="s">
@@ -901,6 +976,9 @@
       <c r="E7" t="s">
         <v>76</v>
       </c>
+      <c r="F7" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="16">
       <c r="A8" s="5" t="s">
@@ -918,6 +996,9 @@
       <c r="E8" t="s">
         <v>78</v>
       </c>
+      <c r="F8" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="16">
       <c r="A9" s="5" t="s">
@@ -935,6 +1016,9 @@
       <c r="E9" t="s">
         <v>80</v>
       </c>
+      <c r="F9" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="16">
       <c r="A10" s="5" t="s">
@@ -952,6 +1036,9 @@
       <c r="E10" t="s">
         <v>82</v>
       </c>
+      <c r="F10" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="16">
       <c r="A11" s="5" t="s">
@@ -969,6 +1056,9 @@
       <c r="E11" t="s">
         <v>84</v>
       </c>
+      <c r="F11" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="16">
       <c r="A12" s="5" t="s">
@@ -986,6 +1076,9 @@
       <c r="E12" t="s">
         <v>86</v>
       </c>
+      <c r="F12" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="16">
       <c r="A13" s="5" t="s">
@@ -1003,6 +1096,9 @@
       <c r="E13" t="s">
         <v>88</v>
       </c>
+      <c r="F13" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="16">
       <c r="A14" s="5" t="s">
@@ -1020,6 +1116,9 @@
       <c r="E14" t="s">
         <v>90</v>
       </c>
+      <c r="F14" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="16">
       <c r="A15" s="5" t="s">
@@ -1037,6 +1136,9 @@
       <c r="E15" t="s">
         <v>92</v>
       </c>
+      <c r="F15" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="16">
       <c r="A16" s="5" t="s">
@@ -1054,8 +1156,11 @@
       <c r="E16" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="16">
+      <c r="F16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16">
       <c r="A17" s="5" t="s">
         <v>21</v>
       </c>
@@ -1071,8 +1176,11 @@
       <c r="E17" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="16">
+      <c r="F17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="16">
       <c r="A18" s="5" t="s">
         <v>22</v>
       </c>
@@ -1088,8 +1196,11 @@
       <c r="E18" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="16">
+      <c r="F18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="16">
       <c r="A19" s="5" t="s">
         <v>23</v>
       </c>
@@ -1105,26 +1216,29 @@
       <c r="E19" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:6">
       <c r="A21" s="2"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>
